--- a/data/trans_camb/IP19C01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 11,83</t>
+          <t>-32,35; 11,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 2,17</t>
+          <t>-40,43; 0,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 41,87</t>
+          <t>10,22; 41,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 8,34</t>
+          <t>-36,66; 6,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 15,66</t>
+          <t>-24,97; 18,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,79; 46,74</t>
+          <t>15,17; 45,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 3,44</t>
+          <t>-28,26; 3,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 1,82</t>
+          <t>-27,86; 2,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,04; 40,11</t>
+          <t>17,14; 39,79</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 19,02</t>
+          <t>-38,71; 16,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,89; 3,36</t>
+          <t>-49,41; -0,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,59; 72,02</t>
+          <t>11,38; 69,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,42; 14,01</t>
+          <t>-46,67; 10,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 28,2</t>
+          <t>-31,19; 32,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,73; 89,59</t>
+          <t>18,57; 85,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 5,29</t>
+          <t>-36,5; 4,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 1,95</t>
+          <t>-35,01; 3,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,05; 68,48</t>
+          <t>20,94; 66,58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 17,08</t>
+          <t>-7,28; 18,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 11,0</t>
+          <t>-15,52; 10,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 3,04</t>
+          <t>-27,33; 1,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 15,01</t>
+          <t>-9,15; 15,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 7,27</t>
+          <t>-18,07; 8,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 4,41</t>
+          <t>-23,84; 5,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 12,72</t>
+          <t>-4,39; 12,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 4,22</t>
+          <t>-13,81; 4,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,7; -0,35</t>
+          <t>-21,64; -0,94</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 24,58</t>
+          <t>-9,16; 26,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 15,77</t>
+          <t>-19,65; 15,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 4,0</t>
+          <t>-33,81; 2,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 22,04</t>
+          <t>-11,12; 22,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 10,5</t>
+          <t>-22,64; 11,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 6,46</t>
+          <t>-30,11; 7,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 18,24</t>
+          <t>-5,48; 17,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 5,8</t>
+          <t>-17,3; 6,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,93; -0,59</t>
+          <t>-27,43; -1,29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 52,44</t>
+          <t>19,13; 54,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 49,08</t>
+          <t>12,14; 48,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,24; 45,45</t>
+          <t>10,49; 48,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 33,32</t>
+          <t>4,13; 31,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 31,48</t>
+          <t>0,28; 30,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 28,63</t>
+          <t>-3,39; 27,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,47; 37,96</t>
+          <t>16,04; 38,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,58; 37,09</t>
+          <t>12,0; 36,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,22; 33,14</t>
+          <t>9,28; 33,24</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,41; 136,76</t>
+          <t>31,13; 144,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,49; 135,7</t>
+          <t>20,26; 130,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,13; 119,19</t>
+          <t>18,96; 137,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,53; 54,92</t>
+          <t>5,26; 52,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 52,42</t>
+          <t>0,39; 49,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 48,39</t>
+          <t>-3,9; 45,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,84; 72,57</t>
+          <t>23,09; 74,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,53; 70,8</t>
+          <t>17,99; 69,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,18; 63,7</t>
+          <t>13,26; 61,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 18,56</t>
+          <t>-16,8; 19,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 11,45</t>
+          <t>-22,9; 11,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 20,92</t>
+          <t>-15,34; 21,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 7,59</t>
+          <t>-21,32; 8,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 6,75</t>
+          <t>-19,57; 6,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 12,71</t>
+          <t>-25,05; 12,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 9,15</t>
+          <t>-14,01; 9,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 5,17</t>
+          <t>-16,49; 6,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 13,28</t>
+          <t>-12,05; 13,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 34,74</t>
+          <t>-23,18; 35,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,5; 22,35</t>
+          <t>-32,48; 21,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 39,19</t>
+          <t>-21,26; 39,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 9,99</t>
+          <t>-24,92; 10,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 9,17</t>
+          <t>-22,89; 9,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 17,4</t>
+          <t>-30,23; 16,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 13,63</t>
+          <t>-18,18; 14,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 7,95</t>
+          <t>-21,91; 9,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 20,26</t>
+          <t>-16,18; 21,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 38,59</t>
+          <t>0,99; 40,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 36,79</t>
+          <t>-10,21; 37,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,18; 50,42</t>
+          <t>19,55; 51,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 35,59</t>
+          <t>-3,46; 34,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 28,02</t>
+          <t>-13,08; 30,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,66; 41,67</t>
+          <t>10,3; 42,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,43; 32,24</t>
+          <t>5,22; 34,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 29,19</t>
+          <t>-4,78; 28,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,19; 41,76</t>
+          <t>19,55; 43,3</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,28; 77,23</t>
+          <t>1,67; 78,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 73,23</t>
+          <t>-12,98; 70,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25,78; 105,2</t>
+          <t>24,52; 105,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 64,64</t>
+          <t>-3,32; 61,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 48,71</t>
+          <t>-16,55; 54,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,73; 77,03</t>
+          <t>12,55; 76,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,58; 57,91</t>
+          <t>7,01; 61,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 51,05</t>
+          <t>-6,2; 49,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>23,82; 74,7</t>
+          <t>25,59; 79,35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,38; 43,91</t>
+          <t>2,25; 41,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,81; 44,72</t>
+          <t>5,6; 43,94</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21,27; 55,81</t>
+          <t>22,92; 56,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 34,73</t>
+          <t>-3,07; 34,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,79; 35,92</t>
+          <t>-0,01; 33,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 31,12</t>
+          <t>-6,6; 31,26</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,05; 30,11</t>
+          <t>4,87; 31,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>7,21; 32,65</t>
+          <t>8,93; 33,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13,73; 39,01</t>
+          <t>14,49; 39,26</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6,17; 109,93</t>
+          <t>4,56; 98,45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4,16; 114,37</t>
+          <t>8,06; 106,28</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28,3; 135,73</t>
+          <t>32,26; 138,95</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 65,62</t>
+          <t>-3,83; 64,97</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,94; 67,73</t>
+          <t>0,15; 62,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 58,88</t>
+          <t>-8,68; 57,33</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,62; 57,91</t>
+          <t>7,12; 60,02</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10,01; 62,26</t>
+          <t>12,29; 66,75</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19,37; 74,55</t>
+          <t>21,57; 76,71</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 18,55</t>
+          <t>-9,61; 18,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,9; 30,83</t>
+          <t>7,63; 31,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 18,86</t>
+          <t>-6,5; 18,88</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,0; 24,5</t>
+          <t>-0,68; 25,48</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,74; 30,94</t>
+          <t>9,76; 33,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 22,48</t>
+          <t>-1,43; 22,56</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 17,56</t>
+          <t>0,25; 17,72</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>11,52; 28,09</t>
+          <t>10,74; 27,42</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 17,09</t>
+          <t>-0,46; 16,81</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 30,36</t>
+          <t>-12,95; 30,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,95; 52,75</t>
+          <t>10,03; 52,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 32,15</t>
+          <t>-9,0; 31,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3,2; 40,81</t>
+          <t>-0,38; 43,63</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,55; 53,91</t>
+          <t>13,61; 56,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 38,51</t>
+          <t>-1,62; 39,47</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 28,58</t>
+          <t>0,4; 28,83</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>16,07; 45,06</t>
+          <t>14,83; 44,81</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,01; 27,2</t>
+          <t>-0,59; 26,96</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 3,05</t>
+          <t>-22,2; 2,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 15,88</t>
+          <t>-7,42; 16,3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>17,86; 36,66</t>
+          <t>18,03; 36,96</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 7,19</t>
+          <t>-15,81; 8,67</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 9,56</t>
+          <t>-15,75; 10,09</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,44; 33,39</t>
+          <t>13,05; 32,63</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 0,75</t>
+          <t>-17,11; 0,75</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 9,78</t>
+          <t>-7,44; 8,22</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>18,36; 31,88</t>
+          <t>18,43; 31,34</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 4,48</t>
+          <t>-30,4; 3,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 25,95</t>
+          <t>-9,99; 27,08</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24,4; 61,64</t>
+          <t>24,37; 63,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-22,48; 10,78</t>
+          <t>-20,9; 14,72</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 15,47</t>
+          <t>-20,94; 15,87</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,17; 55,02</t>
+          <t>17,26; 53,2</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 0,79</t>
+          <t>-23,56; 1,15</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 15,28</t>
+          <t>-10,52; 12,89</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>25,18; 50,74</t>
+          <t>25,43; 49,52</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 11,17</t>
+          <t>0,94; 11,22</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,01; 13,36</t>
+          <t>1,86; 13,3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9,99; 20,71</t>
+          <t>10,16; 20,82</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,78</t>
+          <t>-0,4; 9,88</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,83</t>
+          <t>-0,88; 9,63</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,87; 16,33</t>
+          <t>5,54; 16,09</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,33; 9,07</t>
+          <t>1,05; 8,78</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,7</t>
+          <t>2,0; 9,95</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9,37; 16,91</t>
+          <t>9,47; 17,08</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,7</t>
+          <t>1,38; 17,72</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2,95; 21,28</t>
+          <t>2,62; 21,13</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>14,47; 32,73</t>
+          <t>14,49; 32,87</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 14,23</t>
+          <t>-0,52; 14,62</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 14,53</t>
+          <t>-1,19; 13,99</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,84; 23,68</t>
+          <t>7,55; 23,58</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,51</t>
+          <t>1,47; 13,1</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,59</t>
+          <t>2,83; 14,96</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>13,38; 25,29</t>
+          <t>13,51; 25,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 11,77</t>
+          <t>-32,04; 11,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 0,68</t>
+          <t>-42,05; -0,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,22; 41,01</t>
+          <t>10,29; 40,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 6,02</t>
+          <t>-34,1; 8,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 18,01</t>
+          <t>-24,88; 17,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 45,86</t>
+          <t>16,85; 48,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 3,44</t>
+          <t>-26,93; 3,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 2,12</t>
+          <t>-28,12; 2,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,14; 39,79</t>
+          <t>17,65; 38,57</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,71; 16,36</t>
+          <t>-38,23; 16,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,41; -0,41</t>
+          <t>-49,54; -1,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,38; 69,51</t>
+          <t>11,47; 68,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,67; 10,07</t>
+          <t>-44,73; 14,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 32,95</t>
+          <t>-31,72; 32,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,57; 85,59</t>
+          <t>21,04; 94,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 4,98</t>
+          <t>-34,22; 4,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 3,15</t>
+          <t>-36,14; 3,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,94; 66,58</t>
+          <t>21,72; 63,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 18,06</t>
+          <t>-8,49; 17,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 10,57</t>
+          <t>-15,38; 12,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 1,65</t>
+          <t>-27,27; 1,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 15,49</t>
+          <t>-9,01; 15,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 8,25</t>
+          <t>-19,04; 7,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 5,38</t>
+          <t>-22,46; 4,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 12,71</t>
+          <t>-4,43; 11,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 4,58</t>
+          <t>-14,64; 4,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,64; -0,94</t>
+          <t>-20,75; -0,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 26,3</t>
+          <t>-9,79; 25,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 15,15</t>
+          <t>-19,12; 17,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 2,0</t>
+          <t>-34,38; 2,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 22,27</t>
+          <t>-11,05; 22,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 11,28</t>
+          <t>-23,6; 11,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 7,66</t>
+          <t>-28,88; 6,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 17,71</t>
+          <t>-5,63; 16,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 6,23</t>
+          <t>-18,03; 7,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,43; -1,29</t>
+          <t>-26,66; -0,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,13; 54,24</t>
+          <t>18,42; 52,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,14; 48,88</t>
+          <t>12,76; 49,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,49; 48,48</t>
+          <t>11,44; 47,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 31,91</t>
+          <t>6,2; 33,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 30,91</t>
+          <t>1,94; 32,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 27,26</t>
+          <t>-1,88; 28,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,04; 38,41</t>
+          <t>16,35; 38,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 36,36</t>
+          <t>12,56; 36,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,28; 33,24</t>
+          <t>9,78; 33,2</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,13; 144,45</t>
+          <t>30,6; 141,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,26; 130,06</t>
+          <t>22,83; 136,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,96; 137,88</t>
+          <t>19,61; 127,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,26; 52,38</t>
+          <t>7,49; 56,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 49,07</t>
+          <t>2,54; 53,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 45,72</t>
+          <t>-2,01; 47,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,09; 74,0</t>
+          <t>24,02; 73,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,99; 69,79</t>
+          <t>19,06; 71,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,26; 61,88</t>
+          <t>14,99; 63,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 19,05</t>
+          <t>-14,21; 19,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 11,66</t>
+          <t>-23,29; 9,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 21,81</t>
+          <t>-13,67; 23,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 8,51</t>
+          <t>-22,79; 6,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 6,96</t>
+          <t>-20,15; 8,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 12,12</t>
+          <t>-26,21; 12,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 9,95</t>
+          <t>-13,04; 10,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 6,53</t>
+          <t>-17,52; 5,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 13,99</t>
+          <t>-12,8; 13,61</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 35,36</t>
+          <t>-20,23; 37,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 21,67</t>
+          <t>-34,25; 17,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 39,85</t>
+          <t>-19,65; 42,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 10,83</t>
+          <t>-26,55; 9,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 9,27</t>
+          <t>-24,17; 11,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 16,66</t>
+          <t>-31,15; 17,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 14,95</t>
+          <t>-17,04; 16,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,91; 9,44</t>
+          <t>-22,55; 8,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 21,48</t>
+          <t>-16,84; 20,98</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 40,07</t>
+          <t>-0,06; 40,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 37,12</t>
+          <t>-11,59; 37,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,55; 51,05</t>
+          <t>19,07; 51,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 34,42</t>
+          <t>-1,6; 35,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 30,88</t>
+          <t>-13,73; 29,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,3; 42,02</t>
+          <t>10,77; 41,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,22; 34,1</t>
+          <t>6,1; 32,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 28,39</t>
+          <t>-3,88; 28,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,55; 43,3</t>
+          <t>17,96; 41,95</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,67; 78,17</t>
+          <t>1,5; 83,2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 70,04</t>
+          <t>-14,51; 69,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24,52; 105,71</t>
+          <t>24,08; 108,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 61,01</t>
+          <t>-1,86; 65,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 54,26</t>
+          <t>-16,66; 50,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,55; 76,22</t>
+          <t>13,85; 79,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,01; 61,21</t>
+          <t>7,95; 57,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 49,13</t>
+          <t>-4,87; 47,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25,59; 79,35</t>
+          <t>22,84; 75,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,25; 41,4</t>
+          <t>2,81; 42,19</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,6; 43,94</t>
+          <t>6,4; 44,7</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22,92; 56,5</t>
+          <t>23,81; 57,09</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 34,05</t>
+          <t>-3,36; 32,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 33,13</t>
+          <t>-1,26; 34,5</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 31,26</t>
+          <t>-4,5; 30,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,87; 31,97</t>
+          <t>4,67; 31,55</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>8,93; 33,94</t>
+          <t>6,94; 33,13</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14,49; 39,26</t>
+          <t>12,57; 38,08</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4,56; 98,45</t>
+          <t>4,28; 100,7</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8,06; 106,28</t>
+          <t>8,87; 108,35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32,26; 138,95</t>
+          <t>33,31; 146,54</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 64,97</t>
+          <t>-4,29; 61,83</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,15; 62,13</t>
+          <t>-1,45; 67,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 57,33</t>
+          <t>-5,54; 56,24</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,12; 60,02</t>
+          <t>7,21; 60,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>12,29; 66,75</t>
+          <t>9,91; 63,52</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21,57; 76,71</t>
+          <t>18,23; 74,41</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 18,39</t>
+          <t>-8,28; 18,08</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,63; 31,11</t>
+          <t>7,47; 30,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 18,88</t>
+          <t>-6,21; 19,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 25,48</t>
+          <t>0,65; 25,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,76; 33,07</t>
+          <t>8,38; 32,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 22,56</t>
+          <t>-1,54; 22,33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,25; 17,72</t>
+          <t>0,7; 17,92</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>10,74; 27,42</t>
+          <t>12,07; 28,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 16,81</t>
+          <t>0,45; 16,97</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 30,61</t>
+          <t>-10,84; 30,15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,03; 52,29</t>
+          <t>10,17; 52,67</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 31,54</t>
+          <t>-8,36; 32,59</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 43,63</t>
+          <t>0,69; 42,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>13,61; 56,71</t>
+          <t>11,05; 54,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 39,47</t>
+          <t>-2,1; 38,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,4; 28,83</t>
+          <t>1,06; 29,15</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>14,83; 44,81</t>
+          <t>17,0; 45,68</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 26,96</t>
+          <t>0,69; 26,88</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 2,08</t>
+          <t>-22,74; 2,24</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 16,3</t>
+          <t>-7,16; 15,74</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>18,03; 36,96</t>
+          <t>17,22; 36,54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 8,67</t>
+          <t>-15,56; 7,96</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 10,09</t>
+          <t>-13,55; 8,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,05; 32,63</t>
+          <t>14,23; 33,71</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 0,75</t>
+          <t>-15,41; 0,79</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 8,22</t>
+          <t>-7,36; 9,16</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>18,43; 31,34</t>
+          <t>18,34; 32,34</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 3,19</t>
+          <t>-31,47; 3,35</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 27,08</t>
+          <t>-9,84; 25,89</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24,37; 63,24</t>
+          <t>23,42; 61,82</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 14,72</t>
+          <t>-21,12; 12,78</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 15,87</t>
+          <t>-17,96; 13,95</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,26; 53,2</t>
+          <t>18,86; 54,89</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 1,15</t>
+          <t>-21,55; 0,97</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 12,89</t>
+          <t>-10,13; 13,99</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>25,43; 49,52</t>
+          <t>24,98; 51,92</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,94; 11,22</t>
+          <t>0,74; 11,59</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,86; 13,3</t>
+          <t>1,68; 13,02</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10,16; 20,82</t>
+          <t>9,77; 20,68</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 9,88</t>
+          <t>-0,91; 9,85</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 9,63</t>
+          <t>-1,17; 9,67</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,54; 16,09</t>
+          <t>5,61; 16,28</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,78</t>
+          <t>1,54; 9,44</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,95</t>
+          <t>2,4; 10,07</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9,47; 17,08</t>
+          <t>9,6; 17,11</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>1,38; 17,72</t>
+          <t>1,16; 18,8</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2,62; 21,13</t>
+          <t>2,48; 20,44</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>14,49; 32,87</t>
+          <t>14,21; 33,0</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,62</t>
+          <t>-1,24; 14,57</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 13,99</t>
+          <t>-1,58; 14,27</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,55; 23,58</t>
+          <t>7,54; 23,78</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,1</t>
+          <t>2,15; 14,41</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,96</t>
+          <t>3,39; 15,07</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>13,51; 25,81</t>
+          <t>13,78; 25,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-14,14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,42</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29,76</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-10,26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-22,11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23,96</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-14,14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,42</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,87</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-12,29</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27,45</t>
+          <t>27,4</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 11,56</t>
+          <t>-33,81; 8,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-42,05; -0,26</t>
+          <t>-23,42; 15,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 40,77</t>
+          <t>15,45; 46,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,1; 8,94</t>
+          <t>-29,46; 11,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 17,8</t>
+          <t>-41,8; 2,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,85; 48,26</t>
+          <t>11,18; 41,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 3,06</t>
+          <t>-27,24; 3,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 2,21</t>
+          <t>-26,24; 1,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,65; 38,57</t>
+          <t>17,93; 40,0</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-20,67%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-6,46%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-13,49%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-29,08%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>31,51%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-20,67%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-6,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>43,64%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>-17,16%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,23; 16,58</t>
+          <t>-45,42; 14,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,54; -1,4</t>
+          <t>-30,51; 28,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 68,81</t>
+          <t>18,46; 89,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 14,76</t>
+          <t>-35,38; 19,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 32,67</t>
+          <t>-48,89; 3,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,04; 94,12</t>
+          <t>12,59; 72,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 4,76</t>
+          <t>-34,71; 5,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,14; 3,26</t>
+          <t>-33,86; 1,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,72; 63,53</t>
+          <t>21,98; 67,96</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-6,06</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-9,06</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,33</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-12,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,06</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,32</t>
+          <t>-9,98</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,6</t>
+          <t>-9,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 17,65</t>
+          <t>-8,7; 15,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 12,19</t>
+          <t>-19,44; 7,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 1,61</t>
+          <t>-22,61; 4,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 15,59</t>
+          <t>-7,08; 17,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 7,52</t>
+          <t>-16,73; 11,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 4,96</t>
+          <t>-23,73; 4,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 11,99</t>
+          <t>-4,71; 12,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 4,84</t>
+          <t>-13,48; 4,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,75; -0,24</t>
+          <t>-19,11; 0,95</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-8,01%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-11,97%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-3,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-15,75%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-8,01%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-12,32%</t>
+          <t>-13,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-13,98%</t>
+          <t>-12,52%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 25,42</t>
+          <t>-10,58; 22,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 17,45</t>
+          <t>-23,91; 10,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,38; 2,72</t>
+          <t>-28,47; 6,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 22,57</t>
+          <t>-8,85; 24,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 11,0</t>
+          <t>-20,53; 15,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 6,69</t>
+          <t>-29,62; 5,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 16,77</t>
+          <t>-5,8; 18,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 7,1</t>
+          <t>-17,1; 5,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,66; -0,41</t>
+          <t>-24,05; 1,14</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18,11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16,85</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13,77</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>35,76</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>32,47</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29,41</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18,11</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>16,85</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,11</t>
+          <t>29,29</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21,42</t>
+          <t>21,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,42; 52,92</t>
+          <t>4,45; 33,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 49,7</t>
+          <t>1,45; 31,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,44; 47,39</t>
+          <t>-2,43; 29,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 33,87</t>
+          <t>18,99; 52,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 32,02</t>
+          <t>12,77; 49,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 28,13</t>
+          <t>10,9; 45,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,35; 38,64</t>
+          <t>15,47; 37,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,56; 36,66</t>
+          <t>12,58; 37,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,78; 33,2</t>
+          <t>9,27; 33,34</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25,24%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23,48%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19,19%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>71,56%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>64,98%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>58,86%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25,24%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,6; 141,54</t>
+          <t>5,53; 54,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,83; 136,96</t>
+          <t>2,08; 52,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,61; 127,82</t>
+          <t>-2,47; 49,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 56,04</t>
+          <t>30,41; 136,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 53,11</t>
+          <t>22,49; 135,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 47,7</t>
+          <t>18,67; 118,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,02; 73,54</t>
+          <t>22,84; 72,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,06; 71,41</t>
+          <t>18,53; 70,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,99; 63,27</t>
+          <t>14,43; 64,2</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-6,67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-6,26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-7,45</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,34</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-6,46</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,89</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-6,67</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-6,26</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,55</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-1,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 19,1</t>
+          <t>-21,93; 7,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 9,56</t>
+          <t>-20,74; 6,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 23,08</t>
+          <t>-27,42; 10,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 6,67</t>
+          <t>-13,0; 18,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 8,48</t>
+          <t>-23,49; 11,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 12,7</t>
+          <t>-14,25; 20,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 10,42</t>
+          <t>-14,26; 9,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 5,3</t>
+          <t>-17,45; 5,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 13,61</t>
+          <t>-15,53; 11,82</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-8,22%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-7,71%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-9,18%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-10,31%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-8,22%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-7,71%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-6,84%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-0,12%</t>
+          <t>-2,07%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 37,59</t>
+          <t>-25,89; 9,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 17,8</t>
+          <t>-24,11; 9,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 42,97</t>
+          <t>-31,6; 15,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 9,09</t>
+          <t>-19,18; 34,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 11,03</t>
+          <t>-32,5; 22,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 17,28</t>
+          <t>-19,8; 39,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 16,12</t>
+          <t>-18,77; 13,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 8,2</t>
+          <t>-22,53; 7,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 20,98</t>
+          <t>-20,41; 18,2</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15,52</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8,83</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>24,69</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>21,56</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>15,45</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>34,26</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15,52</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,83</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,48</t>
+          <t>34,15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29,54</t>
+          <t>29,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 40,89</t>
+          <t>-2,4; 35,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 37,58</t>
+          <t>-13,41; 28,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,07; 51,36</t>
+          <t>11,16; 41,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 35,88</t>
+          <t>-0,02; 38,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 29,66</t>
+          <t>-10,08; 36,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,77; 41,74</t>
+          <t>19,01; 50,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,1; 32,89</t>
+          <t>5,43; 32,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 28,21</t>
+          <t>-3,37; 29,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,96; 41,95</t>
+          <t>18,52; 41,86</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>21,51%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>34,23%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>33,66%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>24,12%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>53,49%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,5; 83,2</t>
+          <t>-1,84; 64,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 69,36</t>
+          <t>-15,71; 48,71</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24,08; 108,24</t>
+          <t>13,48; 77,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 65,65</t>
+          <t>0,28; 77,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 50,4</t>
+          <t>-12,35; 73,23</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,85; 79,32</t>
+          <t>25,61; 104,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,95; 57,65</t>
+          <t>7,58; 57,91</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 47,93</t>
+          <t>-3,57; 51,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>22,84; 75,19</t>
+          <t>23,55; 74,8</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>15,27</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>16,91</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>14,23</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>22,33</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>24,05</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>39,42</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>15,27</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>16,91</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,37</t>
+          <t>39,44</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26,12</t>
+          <t>27,07</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,81; 42,19</t>
+          <t>-1,41; 34,73</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,4; 44,7</t>
+          <t>0,79; 35,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23,81; 57,09</t>
+          <t>-4,05; 31,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 32,91</t>
+          <t>4,38; 43,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 34,5</t>
+          <t>2,81; 44,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 30,36</t>
+          <t>21,33; 55,76</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,67; 31,55</t>
+          <t>6,05; 30,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>6,94; 33,13</t>
+          <t>7,21; 32,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12,57; 38,08</t>
+          <t>15,06; 39,5</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>25,55%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>21,5%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>39,61%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>42,67%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>69,93%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>23,07%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4,28; 100,7</t>
+          <t>-1,38; 65,62</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8,87; 108,35</t>
+          <t>1,94; 67,73</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33,31; 146,54</t>
+          <t>-5,42; 59,3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 61,83</t>
+          <t>6,17; 109,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 67,19</t>
+          <t>4,16; 114,37</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 56,24</t>
+          <t>28,25; 135,97</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,21; 60,56</t>
+          <t>8,62; 57,91</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9,91; 63,52</t>
+          <t>10,01; 62,26</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18,23; 74,41</t>
+          <t>20,92; 75,21</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>13,26</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>20,81</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>10,35</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>4,96</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>19,03</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>13,26</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>20,81</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,26</t>
+          <t>4,49</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,4</t>
+          <t>7,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 18,08</t>
+          <t>2,0; 24,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,47; 30,61</t>
+          <t>8,74; 30,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 19,9</t>
+          <t>-1,21; 22,49</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,65; 25,16</t>
+          <t>-6,71; 18,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,38; 32,25</t>
+          <t>7,9; 30,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 22,33</t>
+          <t>-8,25; 17,17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,7; 17,92</t>
+          <t>-0,84; 17,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>12,07; 28,2</t>
+          <t>11,52; 28,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,45; 16,97</t>
+          <t>-0,63; 16,6</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>19,86%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>7,31%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>28,03%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>19,86%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 30,15</t>
+          <t>3,2; 40,81</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,17; 52,67</t>
+          <t>12,55; 53,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 32,59</t>
+          <t>-1,42; 38,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,69; 42,07</t>
+          <t>-8,94; 30,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,05; 54,9</t>
+          <t>10,95; 52,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 38,06</t>
+          <t>-10,81; 28,8</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,06; 29,15</t>
+          <t>-0,78; 28,58</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>17,0; 45,68</t>
+          <t>16,07; 45,06</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,69; 26,88</t>
+          <t>-0,81; 26,71</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-3,99</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-2,15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>23,56</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-10,05</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>3,77</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>26,99</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-3,99</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,48</t>
+          <t>27,34</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>25,15</t>
+          <t>25,37</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 2,24</t>
+          <t>-16,42; 7,19</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 15,74</t>
+          <t>-14,35; 9,56</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>17,22; 36,54</t>
+          <t>14,57; 33,51</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 7,96</t>
+          <t>-21,06; 3,05</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 8,87</t>
+          <t>-8,36; 15,88</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,23; 33,71</t>
+          <t>18,4; 36,99</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 0,79</t>
+          <t>-15,88; 0,75</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 9,16</t>
+          <t>-7,06; 9,78</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>18,34; 32,34</t>
+          <t>18,56; 32,01</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-5,77%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-3,11%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>34,12%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-14,82%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>5,56%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-5,77%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-3,11%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 3,35</t>
+          <t>-22,48; 10,78</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 25,89</t>
+          <t>-18,85; 15,47</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23,42; 61,82</t>
+          <t>19,42; 55,11</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 12,78</t>
+          <t>-29,21; 4,48</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 13,95</t>
+          <t>-11,46; 25,95</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,86; 54,89</t>
+          <t>25,11; 62,34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 0,97</t>
+          <t>-22,23; 0,79</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 13,99</t>
+          <t>-9,82; 15,28</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24,98; 51,92</t>
+          <t>25,5; 51,2</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>4,59</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>4,54</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>11,17</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>5,96</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>7,4</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>15,5</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>4,54</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,03</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>13,42</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,74; 11,59</t>
+          <t>-1,05; 9,78</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,68; 13,02</t>
+          <t>-1,1; 9,83</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9,77; 20,68</t>
+          <t>6,09; 16,38</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 9,85</t>
+          <t>-0,07; 11,17</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 9,67</t>
+          <t>2,01; 13,36</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,61; 16,28</t>
+          <t>10,6; 21,07</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,44</t>
+          <t>1,33; 9,07</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,07</t>
+          <t>2,2; 9,7</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9,6; 17,11</t>
+          <t>9,77; 17,07</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>9,0%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>11,19%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>23,43%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>1,16; 18,8</t>
+          <t>-1,45; 14,23</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2,48; 20,44</t>
+          <t>-1,2; 14,53</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>14,21; 33,0</t>
+          <t>8,16; 24,03</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 14,57</t>
+          <t>0,0; 17,7</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 14,27</t>
+          <t>2,95; 21,28</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,54; 23,78</t>
+          <t>15,44; 33,75</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,15; 14,41</t>
+          <t>1,91; 13,51</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,07</t>
+          <t>3,11; 14,59</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>13,78; 25,87</t>
+          <t>13,74; 25,42</t>
         </is>
       </c>
     </row>
